--- a/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar</t>
+          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,21</t>
+          <t>2,96; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,27 +726,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,77</t>
+          <t>2,51; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 2,87</t>
+          <t>2,64; 2,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,26</t>
+          <t>2,96; 3,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,13</t>
+          <t>2,84; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 2,94</t>
+          <t>2,7; 2,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,14</t>
+          <t>2,94; 3,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 2,81</t>
+          <t>2,62; 2,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,84</t>
+          <t>2,69; 2,84</t>
         </is>
       </c>
     </row>
@@ -861,17 +861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,2</t>
+          <t>2,96; 3,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,08</t>
+          <t>2,82; 3,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,76</t>
+          <t>2,52; 2,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 3,41</t>
+          <t>3,12; 3,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,03</t>
+          <t>2,78; 3,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,22 +896,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,15</t>
+          <t>2,96; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,26</t>
+          <t>3,08; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,01</t>
+          <t>2,85; 3,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 2,83</t>
+          <t>2,66; 2,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,29</t>
+          <t>3,09; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,25</t>
+          <t>3,05; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,03</t>
+          <t>2,82; 3,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,69</t>
+          <t>2,59; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,62</t>
+          <t>3,22; 3,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,25</t>
+          <t>2,91; 3,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,04</t>
+          <t>2,64; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,84</t>
+          <t>2,5; 2,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,34</t>
+          <t>3,15; 3,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,21</t>
+          <t>3,03; 3,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,01</t>
+          <t>2,81; 3,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,62</t>
+          <t>2,62; 3,56</t>
         </is>
       </c>
     </row>
@@ -1141,32 +1141,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,2</t>
+          <t>3,06; 3,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,0</t>
+          <t>2,85; 2,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 2,69</t>
+          <t>2,53; 2,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,4</t>
+          <t>3,19; 3,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,41</t>
+          <t>3,22; 3,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,08</t>
+          <t>2,89; 3,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,01</t>
+          <t>2,9; 3,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,82</t>
+          <t>2,68; 2,83</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,31</t>
+          <t>3,01; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,26</t>
+          <t>3,04; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 2,99</t>
+          <t>2,77; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,75</t>
+          <t>2,51; 2,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,46</t>
+          <t>3,22; 3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 3,31</t>
+          <t>3,08; 3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,06</t>
+          <t>2,88; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 2,79</t>
+          <t>2,5; 2,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 3,25</t>
+          <t>3,1; 3,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,76</t>
+          <t>2,53; 2,75</t>
         </is>
       </c>
     </row>
@@ -1421,27 +1421,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 3,85</t>
+          <t>3,58; 3,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 3,77</t>
+          <t>3,44; 3,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,69</t>
+          <t>3,27; 3,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,2</t>
+          <t>3,05; 3,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,13</t>
+          <t>2,96; 3,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 2,84</t>
+          <t>2,64; 2,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,32</t>
+          <t>3,2; 3,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,1; 3,24</t>
+          <t>3,09; 3,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,01</t>
+          <t>2,82; 3,0</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,21</t>
+          <t>3,13; 3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,21</t>
+          <t>3,12; 3,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 2,99</t>
+          <t>2,89; 2,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,08</t>
+          <t>2,69; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 2,97</t>
+          <t>2,87; 2,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 2,93</t>
+          <t>2,73; 2,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,19</t>
+          <t>2,96; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,21</t>
+          <t>2,95; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 2,87</t>
+          <t>2,62; 2,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,25</t>
+          <t>2,97; 3,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,15</t>
+          <t>2,85; 3,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 2,96</t>
+          <t>2,69; 2,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,18</t>
+          <t>2,99; 3,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 3,13</t>
+          <t>2,95; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 2,81</t>
+          <t>2,63; 2,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 2,84</t>
+          <t>2,68; 2,83</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,01</t>
+          <t>2,76; 3,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,2</t>
+          <t>2,95; 3,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,07</t>
+          <t>2,82; 3,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 2,75</t>
+          <t>2,53; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,34</t>
+          <t>3,08; 3,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,27 +886,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,02</t>
+          <t>2,79; 3,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 2,96</t>
+          <t>2,75; 2,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,14</t>
+          <t>2,95; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,25</t>
+          <t>3,06; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,03</t>
+          <t>2,84; 3,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,68</t>
         </is>
       </c>
     </row>
@@ -1001,57 +1001,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,24</t>
+          <t>3,04; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,05</t>
+          <t>2,83; 3,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,66</t>
+          <t>2,57; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 3,61</t>
+          <t>3,23; 3,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,22</t>
+          <t>2,91; 3,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,02</t>
+          <t>2,62; 3,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,84</t>
+          <t>2,53; 2,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,34</t>
+          <t>3,16; 3,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,21</t>
+          <t>3,04; 3,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,01</t>
+          <t>2,81; 3,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,56</t>
+          <t>2,59; 2,79</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 2,99</t>
+          <t>2,85; 3,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,7</t>
+          <t>2,57; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 3,41</t>
+          <t>3,23; 3,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 2,96</t>
+          <t>2,8; 2,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,25</t>
+          <t>3,12; 3,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,26</t>
+          <t>3,14; 3,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,01</t>
+          <t>2,89; 3,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,83</t>
+          <t>2,69; 2,8</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,67</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,3</t>
+          <t>3,03; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,27</t>
+          <t>3,03; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 2,99</t>
+          <t>2,76; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,76</t>
+          <t>2,52; 2,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 3,46</t>
+          <t>3,21; 3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,29</t>
+          <t>3,09; 3,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,08</t>
+          <t>2,88; 3,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,81</t>
+          <t>2,63; 2,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 3,26</t>
+          <t>3,09; 3,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,75</t>
+          <t>2,6; 2,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,93</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 3,94</t>
+          <t>3,7; 3,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,58; 3,83</t>
+          <t>3,58; 3,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,79</t>
+          <t>3,45; 3,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,71</t>
+          <t>3,25; 3,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,21</t>
+          <t>3,06; 3,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 2,96</t>
+          <t>2,79; 2,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 2,84</t>
+          <t>2,7; 2,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,33</t>
+          <t>3,19; 3,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,24</t>
+          <t>3,1; 3,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,0</t>
+          <t>2,84; 3,03</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -1556,42 +1556,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3,12; 3,21</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>3,13; 3,21</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>3,12; 3,22</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 2,98</t>
+          <t>2,9; 2,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,05</t>
+          <t>2,67; 2,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,26</t>
+          <t>3,17; 3,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 3,2</t>
+          <t>3,1; 3,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 2,96</t>
+          <t>2,88; 2,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 2,82</t>
+          <t>2,75; 2,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,19</t>
+          <t>3,12; 3,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 2,94</t>
+          <t>2,72; 2,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
+          <t>Número medio de personas que conviven habitualmente en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
